--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38014</v>
+        <v>69.3</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.3</v>
+        <v>38014</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -487,7 +487,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,7 +529,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,11 +599,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -627,11 +627,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -641,11 +641,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -655,7 +655,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -669,7 +669,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -683,7 +683,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -695,13 +695,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -709,11 +709,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>45900</v>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>43239</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -722,10 +724,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -734,10 +736,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -746,10 +748,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -758,10 +760,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -770,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -782,10 +784,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -794,10 +796,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -806,10 +808,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -818,10 +820,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -830,10 +832,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -842,10 +844,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -854,10 +856,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -866,10 +868,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -878,10 +880,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -890,10 +892,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -902,10 +904,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -914,10 +916,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -926,10 +928,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -938,10 +940,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -950,10 +952,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -962,10 +964,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -974,10 +976,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -986,7 +988,7 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B45" s="1" t="n">
         <v>35700</v>
@@ -998,10 +1000,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1010,10 +1012,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1022,10 +1024,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1034,10 +1036,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1046,10 +1048,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1058,10 +1060,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1070,10 +1072,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1082,10 +1084,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1094,10 +1096,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1106,10 +1108,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1118,10 +1120,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1130,10 +1132,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1142,10 +1144,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1154,10 +1156,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1166,10 +1168,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1178,10 +1180,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1190,10 +1192,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1202,10 +1204,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1214,10 +1216,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1226,10 +1228,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1238,10 +1240,10 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
@@ -1250,10 +1252,10 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C67">
         <f>(B67/B79-1)*100</f>
@@ -1262,10 +1264,10 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C68">
         <f>(B68/B80-1)*100</f>
@@ -1273,7 +1275,12 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n"/>
+      <c r="A69" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C69">
         <f>(B69/B81-1)*100</f>
         <v/>
@@ -1358,6 +1365,13 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
+      <c r="C81">
+        <f>(B81/B93-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
